--- a/data/trans_orig/IP29_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP29_R-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18879</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33323</t>
+          <t>33372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>20837</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35318</t>
+          <t>35001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43689</t>
+          <t>44864</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63043</t>
+          <t>64596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65529</t>
+          <t>65480</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79973</t>
+          <t>79769</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>59202</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73322</t>
+          <t>73366</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130012</t>
+          <t>128459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149366</t>
+          <t>148191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33279</t>
+          <t>33241</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16738</t>
+          <t>16254</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29462</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38629</t>
+          <t>39485</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57277</t>
+          <t>57446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49645</t>
+          <t>49683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63181</t>
+          <t>64298</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54519</t>
+          <t>54933</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67243</t>
+          <t>67727</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109627</t>
+          <t>109458</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>128275</t>
+          <t>127419</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,34%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>13486</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24863</t>
+          <t>24655</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,47 +1433,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>20,63%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>37,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>26683</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19661</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>33666</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>28,08%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>20,69%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>26683</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>20242</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>33881</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>28,08%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>21,3%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>36453</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55216</t>
+          <t>55058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40522</t>
+          <t>40730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51856</t>
+          <t>51899</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,49 +1546,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>79,37%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>68341</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>61358</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>75363</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>71,92%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>64,57%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>79,31%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>68341</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61143</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>74782</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>71,92%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>64,34%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>78,7%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>173</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105193</t>
+          <t>105351</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124528</t>
+          <t>123956</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45732</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66017</t>
+          <t>64220</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46406</t>
+          <t>46735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66310</t>
+          <t>66588</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97962</t>
+          <t>97123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126513</t>
+          <t>125031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126028</t>
+          <t>127825</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146313</t>
+          <t>146562</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>125906</t>
+          <t>125628</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>145810</t>
+          <t>145481</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>257749</t>
+          <t>259231</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>286300</t>
+          <t>287139</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,72%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27558</t>
+          <t>28575</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43646</t>
+          <t>43779</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27026</t>
+          <t>27429</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42839</t>
+          <t>43823</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59901</t>
+          <t>58034</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82174</t>
+          <t>82239</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54960</t>
+          <t>54827</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71048</t>
+          <t>70031</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81632</t>
+          <t>80648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>97445</t>
+          <t>97042</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140903</t>
+          <t>140838</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>163176</t>
+          <t>165043</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,98%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>24779</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16951</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29486</t>
+          <t>29586</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45448</t>
+          <t>45832</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64472</t>
+          <t>64687</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,5%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>34607</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48467</t>
+          <t>48626</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39292</t>
+          <t>39192</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51827</t>
+          <t>51520</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77711</t>
+          <t>77496</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96735</t>
+          <t>96351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,77%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>173340</t>
+          <t>173919</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>210606</t>
+          <t>211152</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>172744</t>
+          <t>171135</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>209735</t>
+          <t>209057</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>357542</t>
+          <t>354780</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>407163</t>
+          <t>409854</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>400611</t>
+          <t>400065</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>437877</t>
+          <t>437298</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>448938</t>
+          <t>449616</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>485929</t>
+          <t>487538</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>862727</t>
+          <t>860036</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>912348</t>
+          <t>915110</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,06%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>25138</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39081</t>
+          <t>40719</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21463</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58830</t>
+          <t>57663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49511</t>
+          <t>47873</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63910</t>
+          <t>63454</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66355</t>
+          <t>66095</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77779</t>
+          <t>77952</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117580</t>
+          <t>118747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>137880</t>
+          <t>138077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,27%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>17927</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31340</t>
+          <t>31586</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21163</t>
+          <t>21284</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30119</t>
+          <t>30136</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48245</t>
+          <t>48184</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59258</t>
+          <t>59012</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72486</t>
+          <t>72671</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72826</t>
+          <t>72705</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84067</t>
+          <t>84373</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136342</t>
+          <t>136403</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154468</t>
+          <t>154451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22044</t>
+          <t>21620</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19785</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37586</t>
+          <t>38365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62080</t>
+          <t>62504</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73530</t>
+          <t>74362</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64329</t>
+          <t>63573</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75051</t>
+          <t>74981</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>130652</t>
+          <t>129873</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146055</t>
+          <t>146493</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42663</t>
+          <t>42879</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63959</t>
+          <t>63948</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49570</t>
+          <t>50239</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71914</t>
+          <t>72167</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98532</t>
+          <t>97591</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129060</t>
+          <t>128459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136237</t>
+          <t>136248</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>157533</t>
+          <t>157317</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>149241</t>
+          <t>148988</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>171585</t>
+          <t>170916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>292291</t>
+          <t>292892</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322819</t>
+          <t>323760</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,84%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37207</t>
+          <t>36735</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55733</t>
+          <t>55440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32548</t>
+          <t>31668</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51180</t>
+          <t>49219</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>74520</t>
+          <t>75641</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99861</t>
+          <t>100468</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91259</t>
+          <t>91552</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109785</t>
+          <t>110257</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87525</t>
+          <t>89486</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106157</t>
+          <t>107037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>185836</t>
+          <t>185229</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>211177</t>
+          <t>210056</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,52%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13492</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>9592</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>21450</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16403</t>
+          <t>16366</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31569</t>
+          <t>31325</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38360</t>
+          <t>37728</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47242</t>
+          <t>47411</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49377</t>
+          <t>49286</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60787</t>
+          <t>61144</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>91019</t>
+          <t>91263</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>106185</t>
+          <t>106222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>161175</t>
+          <t>161608</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>199641</t>
+          <t>199457</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>142950</t>
+          <t>141319</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>178226</t>
+          <t>178751</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>314119</t>
+          <t>311141</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>369387</t>
+          <t>364327</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>462713</t>
+          <t>462897</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>501179</t>
+          <t>500746</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>518289</t>
+          <t>517764</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>553565</t>
+          <t>555196</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>989483</t>
+          <t>994543</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1044751</t>
+          <t>1047729</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,1%</t>
         </is>
       </c>
     </row>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19420</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33687</t>
+          <t>33303</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23478</t>
+          <t>23835</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39256</t>
+          <t>38042</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47308</t>
+          <t>46504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67054</t>
+          <t>66807</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47482</t>
+          <t>47866</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61548</t>
+          <t>61749</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54369</t>
+          <t>55583</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70147</t>
+          <t>69790</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107740</t>
+          <t>107987</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127486</t>
+          <t>128290</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34149</t>
+          <t>34769</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37692</t>
+          <t>38404</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45978</t>
+          <t>45113</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66340</t>
+          <t>66634</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68193</t>
+          <t>67573</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82956</t>
+          <t>82950</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72258</t>
+          <t>71546</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87546</t>
+          <t>86614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145952</t>
+          <t>145658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166314</t>
+          <t>167179</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,75%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9534</t>
+          <t>9572</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19980</t>
+          <t>20013</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13142</t>
+          <t>13594</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>26600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25792</t>
+          <t>26061</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42353</t>
+          <t>42488</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40546</t>
+          <t>40513</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50992</t>
+          <t>50954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49893</t>
+          <t>48828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62286</t>
+          <t>61834</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93601</t>
+          <t>93466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110162</t>
+          <t>109893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59840</t>
+          <t>59890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81870</t>
+          <t>83190</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54149</t>
+          <t>53221</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76694</t>
+          <t>76240</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119439</t>
+          <t>120553</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151061</t>
+          <t>150260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,63%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135105</t>
+          <t>133785</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>157135</t>
+          <t>157085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>128093</t>
+          <t>128547</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>150638</t>
+          <t>151566</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>270701</t>
+          <t>271502</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>302323</t>
+          <t>301209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,42%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24304</t>
+          <t>25480</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39974</t>
+          <t>40483</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35748</t>
+          <t>35262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54649</t>
+          <t>53932</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65089</t>
+          <t>64528</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89096</t>
+          <t>88914</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93715</t>
+          <t>93206</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109385</t>
+          <t>108209</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>87117</t>
+          <t>87834</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>106504</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186359</t>
+          <t>186541</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>210366</t>
+          <t>210927</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,57%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16467</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28365</t>
+          <t>28448</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16742</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29426</t>
+          <t>30103</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36330</t>
+          <t>36472</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54214</t>
+          <t>54754</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,92%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32052</t>
+          <t>31969</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43950</t>
+          <t>44299</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37728</t>
+          <t>37051</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50250</t>
+          <t>50412</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73357</t>
+          <t>72817</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>91241</t>
+          <t>91099</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,41%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>174319</t>
+          <t>170402</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>211110</t>
+          <t>208451</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>190677</t>
+          <t>194473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>233154</t>
+          <t>234340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>375478</t>
+          <t>375654</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>432483</t>
+          <t>429928</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>444008</t>
+          <t>446667</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>480799</t>
+          <t>484716</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>459555</t>
+          <t>458369</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>502032</t>
+          <t>498236</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>915344</t>
+          <t>917899</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>972349</t>
+          <t>972173</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,13%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP29_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP29_R-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>27553</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21505</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35889</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29,25%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>38,1%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>25534</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19083</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33372</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>18508</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>33323</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>25,83%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,3%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>27553</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>20837</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>35001</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>29,25%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44864</t>
+          <t>44089</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64596</t>
+          <t>63698</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66650</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>58314</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>72698</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>70,75%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>61,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77,17%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>73318</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>65480</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>79769</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>65529</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>80344</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>74,17%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>66,24%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>80,7%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66650</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>59202</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>73366</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>70,75%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128459</t>
+          <t>129357</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148191</t>
+          <t>148966</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>77,16%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>94203</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>94203</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>94203</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>98852</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>98852</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>98852</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>94203</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>94203</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>94203</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22291</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16031</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>28750</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>26,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>19,09%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>34,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>25654</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>18626</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>33241</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>19108</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>32432</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>30,94%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>22,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>40,09%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>22291</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>16254</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>29048</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>26,54%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39485</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57446</t>
+          <t>58300</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>61690</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>55231</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>67950</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>73,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>65,77%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>80,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>57270</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>49683</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>64298</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>50492</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>63816</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>69,06%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>59,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>61690</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>54933</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>67727</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>73,46%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109458</t>
+          <t>108604</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>127419</t>
+          <t>128489</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,98%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>83981</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>83981</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>83981</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>82924</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>82924</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>82924</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>83981</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>83981</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>83981</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26683</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19381</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33684</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>28,08%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,45%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>18602</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13486</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24655</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13433</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>24986</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>28,45%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>26683</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>19661</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>33666</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>28,08%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36453</t>
+          <t>35832</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55058</t>
+          <t>55531</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>68341</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>61340</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>75643</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>71,92%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>79,6%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>46783</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>40730</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>51899</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>40399</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>51952</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>71,55%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>79,37%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>68341</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>61358</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>75363</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>71,92%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>105351</t>
+          <t>104878</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123956</t>
+          <t>124577</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>95024</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>95024</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>95024</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>65385</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>65385</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>65385</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>95024</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>95024</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>95024</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>55988</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>47012</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>67039</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>29,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>24,46%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>34,88%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>54980</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>45483</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>64220</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>45395</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>65613</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>28,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>23,68%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>33,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>55988</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>46735</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>66588</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>29,13%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97123</t>
+          <t>96862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125031</t>
+          <t>124855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>136228</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>125177</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>145204</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>70,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>65,12%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>75,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>137065</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>127825</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>146562</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>126432</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>146650</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>71,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>66,56%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>76,32%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>136228</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>125628</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>145481</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>70,87%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>259231</t>
+          <t>259407</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>287139</t>
+          <t>287400</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>74,79%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>192216</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>192216</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>192216</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>291</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192045</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192045</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192045</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>192216</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>192216</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>192216</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2099,67 +2099,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>34661</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27167</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>43161</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>27,85%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>21,83%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>34,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>35807</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28575</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>43779</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>28042</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>43615</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>36,31%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28,98%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>44,4%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>34661</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>27429</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>43823</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>27,85%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58034</t>
+          <t>60520</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82239</t>
+          <t>83151</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>89810</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>81310</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>97304</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>72,15%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>65,32%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>78,17%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>62799</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>54827</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>70031</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>54991</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>63,69%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>55,6%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>71,02%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>89810</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>80648</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>97042</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>72,15%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140838</t>
+          <t>139926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>165043</t>
+          <t>162557</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>72,87%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>124471</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>124471</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>124471</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>98606</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>98606</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>98606</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>124471</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>124471</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>124471</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,72 +2437,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>22948</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>16524</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>29521</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>33,37%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>24,03%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>42,92%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>31419</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>24779</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>38798</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>24463</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>38213</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>42,8%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>33,76%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>52,86%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>22948</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>17258</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>29586</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>33,37%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45832</t>
+          <t>45034</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64687</t>
+          <t>64813</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -2550,72 +2550,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>45830</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>39257</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>52254</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>66,63%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>57,08%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>75,97%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>41986</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>34607</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>48626</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>35192</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>57,2%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>47,14%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>66,24%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>45830</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>39192</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>51520</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>66,63%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77496</t>
+          <t>77370</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96351</t>
+          <t>97149</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,33%</t>
         </is>
       </c>
     </row>
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68778</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>68778</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>68778</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>73405</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>73405</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>73405</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>68778</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>68778</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>68778</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>190124</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>173645</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>208841</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>28,86%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>26,36%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>31,71%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>191996</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>173919</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>211152</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>172484</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>210110</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>31,41%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>28,45%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>34,55%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>190124</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>171135</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>209057</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>28,86%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>354780</t>
+          <t>354579</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>409854</t>
+          <t>408546</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>468549</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>449832</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>485028</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>71,14%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>68,29%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>73,64%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>419221</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>400065</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>437298</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>401107</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>438733</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>68,59%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>65,45%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>71,55%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>468549</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>449616</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>487538</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>71,14%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>860036</t>
+          <t>861344</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>915110</t>
+          <t>915311</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,08%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>991</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>658673</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>658673</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>658673</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>913</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>611217</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>611217</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>611217</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>991</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>658673</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>658673</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>658673</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,72 +3357,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15304</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9734</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21410</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,43%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,38%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>32266</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25138</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40719</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>24741</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40162</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>36,42%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45,96%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>15304</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9866</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21723</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17,43%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38260</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57663</t>
+          <t>58815</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -3470,72 +3470,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>72514</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>66408</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>78084</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,57%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>56326</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>47873</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>63454</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48430</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>63851</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>63,58%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>54,04%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>71,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>72514</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>66095</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>77952</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>82,57%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118747</t>
+          <t>117595</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>138077</t>
+          <t>138150</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>87818</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>87818</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>87818</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88592</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88592</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88592</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>87818</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>87818</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>87818</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,72 +3700,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14825</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9577</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21215</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,19%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,57%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>24507</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17927</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>31586</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>18111</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>31498</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>27,05%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19,79%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14825</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9616</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>21284</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30136</t>
+          <t>31280</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48184</t>
+          <t>49802</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -3813,72 +3813,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>79164</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>72774</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>84412</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,43%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>89,81%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>66091</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>59012</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>72671</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>59100</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>72487</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>72,95%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>65,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>79164</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>72705</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>84373</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>84,23%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136403</t>
+          <t>134785</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154451</t>
+          <t>153307</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>93989</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>93989</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>93989</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>90598</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>90598</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>90598</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>93989</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>93989</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>93989</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4043,72 +4043,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13829</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19955</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,72%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>15585</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9762</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>21620</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10433</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21687</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>18,53%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,6%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13829</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9133</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>20541</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,44%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>21942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>37881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -4156,72 +4156,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70285</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>64159</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>74906</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76,28%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68539</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>62504</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>74362</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>62437</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>73691</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>81,47%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>74,3%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,4%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70285</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>63573</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>74981</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>83,56%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129873</t>
+          <t>130357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146493</t>
+          <t>146296</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,96%</t>
         </is>
       </c>
     </row>
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>84114</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>84114</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>84114</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>84124</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>84124</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>84124</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>84114</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>84114</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>84114</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,72 +4386,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>59735</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>48214</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>70523</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27,01%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>52402</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>42879</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>63948</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>43083</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>63136</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>26,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>31,94%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>59735</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>50239</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>72167</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>27,01%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97591</t>
+          <t>95811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128459</t>
+          <t>126362</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -4499,72 +4499,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>161420</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>150632</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>172941</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>72,99%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>78,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>147794</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>136248</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>157317</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>137060</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>157113</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>73,82%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>68,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>78,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>161420</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>148988</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>170916</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>72,99%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>292892</t>
+          <t>294989</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>323760</t>
+          <t>325540</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>77,26%</t>
         </is>
       </c>
     </row>
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>221155</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>221155</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>221155</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>290</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200196</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200196</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200196</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>221155</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>221155</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>221155</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>40931</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>32842</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>50430</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>29,51%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>23,68%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>36,36%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>45550</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>36735</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>55440</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>35264</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>54689</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>30,99%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,99%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>37,72%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>40931</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>31668</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>49219</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>29,51%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75641</t>
+          <t>73127</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100468</t>
+          <t>100207</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -4842,72 +4842,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>97774</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>88275</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>105863</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>70,49%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>63,64%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>76,32%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>101442</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>91552</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>110257</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>92303</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>111728</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>69,01%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>62,28%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>75,01%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>97774</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>89486</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>107037</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>70,49%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>185229</t>
+          <t>185490</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>210056</t>
+          <t>212570</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>74,4%</t>
         </is>
       </c>
     </row>
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>138705</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>138705</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>138705</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>146992</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>146992</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>146992</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>138705</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>138705</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>138705</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14761</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9559</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>21808</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>20,87%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>13,51%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>30,83%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>8333</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>4441</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>14124</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>13871</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>16,07%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>8,56%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>27,24%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>14761</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>9592</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>21450</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>20,87%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>13,56%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16366</t>
+          <t>15929</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31325</t>
+          <t>31628</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -5185,74 +5185,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>55975</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>48928</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>61177</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>79,13%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>69,17%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>86,49%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>43519</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>37728</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>37981</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>47411</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>83,93%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>72,76%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>73,25%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>91,44%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>55975</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>49286</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>61144</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>79,13%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>69,68%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>86,44%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>144</t>
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>91263</t>
+          <t>90960</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>106222</t>
+          <t>106659</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>70736</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>70736</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>70736</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>51852</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>51852</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>51852</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>70736</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>70736</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>70736</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>159384</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>140605</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>178350</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>22,88%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>20,19%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>25,61%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>178645</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>161608</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>199457</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>159772</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>198345</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>26,97%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>30,11%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>159384</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>141319</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>178751</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>22,88%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>311141</t>
+          <t>313121</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>364327</t>
+          <t>363551</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -5528,72 +5528,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>537131</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>518165</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>555910</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>77,12%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>74,39%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>79,81%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>701</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>483709</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>462897</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>500746</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>464009</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>502582</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>73,03%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>69,89%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>75,6%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>775</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>537131</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>517764</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>555196</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>77,12%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>994543</t>
+          <t>995319</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1047729</t>
+          <t>1045749</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,96%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>696515</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>696515</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>696515</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>956</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>662354</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>662354</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>662354</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>696515</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>696515</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>696515</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,72 +5992,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30652</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23797</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>39371</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>32,74%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>25,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>25759</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19420</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33303</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19132</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>32773</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>31,74%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>41,03%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>30652</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>23835</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>38042</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>32,74%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46504</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66807</t>
+          <t>66961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,31%</t>
         </is>
       </c>
     </row>
@@ -6105,72 +6105,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>62973</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>54254</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>69828</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>67,26%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>57,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>74,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55410</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>47866</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>61749</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48396</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>62037</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>68,26%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>58,97%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>76,07%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>62973</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55583</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>69790</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>67,26%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107987</t>
+          <t>107833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128290</t>
+          <t>128387</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,45%</t>
         </is>
       </c>
     </row>
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>93625</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>93625</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>93625</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>81169</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>81169</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>81169</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>93625</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>93625</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>93625</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6335,72 +6335,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29779</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22573</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37741</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>27,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>20,53%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>34,33%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>26001</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>19392</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>34769</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>19036</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>33870</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>25,41%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,95%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>33,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>29779</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>23336</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>38404</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>27,08%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45113</t>
+          <t>45560</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66634</t>
+          <t>65991</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -6448,72 +6448,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>80171</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>72209</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87377</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>72,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>65,67%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>79,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>76341</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>67573</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>82950</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>68472</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>83306</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>74,59%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>80171</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>71546</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>86614</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>72,92%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145658</t>
+          <t>146301</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>167179</t>
+          <t>166732</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,54%</t>
         </is>
       </c>
     </row>
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>109950</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>109950</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>109950</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>102342</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>102342</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>102342</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>109950</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>109950</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>109950</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6678,72 +6678,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19344</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13962</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>26395</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>25,65%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>18,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>34,99%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>14268</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9572</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20013</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9058</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20202</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>23,57%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>19344</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>13594</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>26600</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>25,65%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42488</t>
+          <t>42406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -6791,72 +6791,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>56084</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>49033</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>61466</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>74,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>65,01%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>81,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>46258</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>40513</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>50954</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>40324</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>51468</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>76,43%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>66,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>84,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>56084</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>48828</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>61834</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>74,35%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93466</t>
+          <t>93548</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109893</t>
+          <t>109586</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>60526</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>60526</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>60526</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>64837</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>54251</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>76688</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,66%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>37,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>70651</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>59890</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>83190</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>60305</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>81515</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>32,56%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>27,6%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>38,34%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>64837</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>53221</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>76240</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>31,66%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120553</t>
+          <t>119233</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150260</t>
+          <t>149821</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>139950</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>128099</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>150536</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>68,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>62,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>73,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>146324</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>133785</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>157085</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>135460</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>156670</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>67,44%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,66%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>139950</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>128547</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>151566</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>68,34%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>271502</t>
+          <t>271941</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>301209</t>
+          <t>302529</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204787</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204787</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204787</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>216975</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>216975</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>216975</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204787</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204787</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204787</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7364,72 +7364,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>44393</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>33881</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>53596</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31,31%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>23,9%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>37,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>32188</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>25480</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>40483</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>24950</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>40259</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>24,08%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>44393</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>35262</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>53932</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>31,31%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64528</t>
+          <t>64466</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88914</t>
+          <t>89622</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -7477,72 +7477,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>97373</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>88170</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>107885</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>68,69%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>62,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>76,1%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>101501</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>93206</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>108209</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>93430</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>108739</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>75,92%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>69,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>80,94%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>97373</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>87834</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>106504</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>68,69%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186541</t>
+          <t>185833</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>210927</t>
+          <t>210989</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,6%</t>
         </is>
       </c>
     </row>
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>141766</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>141766</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>141766</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>133689</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>133689</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>133689</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>141766</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>141766</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>141766</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7707,72 +7707,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>22867</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17080</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>29915</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>34,05%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>25,43%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>44,55%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>22015</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>16118</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>28448</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>16227</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>28739</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>36,44%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>26,68%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>47,09%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>22867</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>16742</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>30103</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>34,05%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>35510</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54754</t>
+          <t>53730</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -7820,72 +7820,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>44287</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>37239</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>50074</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>65,95%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>55,45%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>74,57%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>38402</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>31969</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>44299</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>31678</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>44190</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>63,56%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>52,91%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>73,32%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>44287</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>37051</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>50412</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>65,95%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72817</t>
+          <t>73841</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>91099</t>
+          <t>92061</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>72,16%</t>
         </is>
       </c>
     </row>
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67154</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67154</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67154</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>60417</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>60417</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>60417</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67154</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67154</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67154</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>211872</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>191512</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>231316</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>30,59%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>27,65%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>33,39%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>289</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>190883</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>170402</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>208451</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>173047</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>209873</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>29,14%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>26,01%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>31,82%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>211872</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>194473</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>234340</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>30,59%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>375654</t>
+          <t>375454</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>429928</t>
+          <t>431836</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>480837</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>461393</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>501197</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>69,41%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>66,61%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>72,35%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>699</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>464235</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>446667</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>484716</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>445245</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>482071</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>70,86%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>68,18%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>73,99%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>480837</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>458369</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>498236</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>69,41%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>917899</t>
+          <t>915991</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>972173</t>
+          <t>972373</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,14%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>692709</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>692709</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>692709</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>988</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>655118</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>655118</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>655118</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>992</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>692709</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>692709</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>692709</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
